--- a/artfynd/A 43201-2023 artfynd.xlsx
+++ b/artfynd/A 43201-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43201-2023 artfynd.xlsx
+++ b/artfynd/A 43201-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95808996</v>
+        <v>95808983</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk lundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scutula effusa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Rabenh.) Kistenich et al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710474.7306489728</v>
+        <v>710636</v>
       </c>
       <c r="R2" t="n">
-        <v>6400973.719540871</v>
+        <v>6400974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +743,22 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -779,17 +769,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,37 +797,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95808995</v>
+        <v>95808991</v>
       </c>
       <c r="B3" t="n">
-        <v>76934</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6435</v>
+        <v>125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskivlav</t>
+          <t>Mörk lundlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplotomma alboatrum</t>
+          <t>Scutula effusa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Flot.</t>
+          <t>(Rabenh.) Kistenich et al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710481.1892300542</v>
+        <v>710435</v>
       </c>
       <c r="R3" t="n">
-        <v>6400993.865816458</v>
+        <v>6401120</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,31 +865,21 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -944,37 +919,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95808988</v>
+        <v>95808993</v>
       </c>
       <c r="B4" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk lundlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scutula effusa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Rabenh.) Kistenich et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710596.7425377097</v>
+        <v>710480</v>
       </c>
       <c r="R4" t="n">
-        <v>6401112.861949743</v>
+        <v>6401017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,32 +987,22 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1053,17 +1013,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,50 +1041,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95808989</v>
+        <v>95823960</v>
       </c>
       <c r="B5" t="n">
-        <v>78840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>226</v>
+        <v>125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Mörk lundlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Scutula effusa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Rabenh.) Kistenich et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lauks änge, Gtl</t>
+          <t>Lauks änge (västra), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710596.7425377097</v>
+        <v>710457</v>
       </c>
       <c r="R5" t="n">
-        <v>6401112.861949743</v>
+        <v>6400980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,19 +1109,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,85 +1128,65 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Ädellövskog/hassellund/lövänge</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Ola Hammarström, Raul Vicente</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95808994</v>
+        <v>95823963</v>
       </c>
       <c r="B6" t="n">
-        <v>79135</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>737</v>
+        <v>125</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mörk lundlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Scutula effusa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(Rabenh.) Kistenich et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lauks änge, Gtl</t>
+          <t>Lauks änge (västra), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>710481.1892300542</v>
+        <v>710476</v>
       </c>
       <c r="R6" t="n">
-        <v>6400993.865816458</v>
+        <v>6400945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,19 +1216,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,80 +1232,55 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Ädellövskog/hassellund/lövänge</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Ola Hammarström, Raul Vicente</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95808993</v>
+        <v>95808989</v>
       </c>
       <c r="B7" t="n">
-        <v>78031</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk lundlav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scutula effusa</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rabenh.) Kistenich et al.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>710479.9912014252</v>
+        <v>710597</v>
       </c>
       <c r="R7" t="n">
-        <v>6401016.824759999</v>
+        <v>6401113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,32 +1323,17 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1459,17 +1344,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1487,50 +1372,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95808991</v>
+        <v>95823917</v>
       </c>
       <c r="B8" t="n">
-        <v>78031</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk lundlav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scutula effusa</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rabenh.) Kistenich et al.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lauks änge, Gtl</t>
+          <t>Lauks änge (västra), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>710434.9169866859</v>
+        <v>710594</v>
       </c>
       <c r="R8" t="n">
-        <v>6401119.941630095</v>
+        <v>6400909</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1560,19 +1440,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 8</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,38 +1456,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Ädellövskog/hassellund/lövänge</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1624,37 +1479,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95823961</v>
+        <v>95823962</v>
       </c>
       <c r="B9" t="n">
-        <v>76934</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6435</v>
+        <v>734</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitskivlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diplotomma alboatrum</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Flot.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1664,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>710475.7280026325</v>
+        <v>710476</v>
       </c>
       <c r="R9" t="n">
-        <v>6400944.325201127</v>
+        <v>6400945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1697,19 +1547,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1746,50 +1586,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95823963</v>
+        <v>95808994</v>
       </c>
       <c r="B10" t="n">
-        <v>78031</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>737</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk lundlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scutula effusa</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Rabenh.) Kistenich et al.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lauks änge (västra), Gtl</t>
+          <t>Lauks änge, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>710475.7280026325</v>
+        <v>710481</v>
       </c>
       <c r="R10" t="n">
-        <v>6400944.325201127</v>
+        <v>6400994</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1819,86 +1654,86 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lauks änge (västra) 10</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95823955</v>
+        <v>95823958</v>
       </c>
       <c r="B11" t="n">
-        <v>77870</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6430</v>
+        <v>737</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slät lönnlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bacidia fraxinea</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lönnr.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1908,13 +1743,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>710513.7985833556</v>
+        <v>710499</v>
       </c>
       <c r="R11" t="n">
-        <v>6401109.067499299</v>
+        <v>6401016</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1938,27 +1773,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 15</t>
+          <t>Lauks änge (västra) 12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,7 +1797,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1990,37 +1815,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95823957</v>
+        <v>95823913</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>738</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2030,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>710552.3153178105</v>
+        <v>710519</v>
       </c>
       <c r="R12" t="n">
-        <v>6401059.682078632</v>
+        <v>6400964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,24 +1883,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 13</t>
+          <t>Lauks änge (västra) 9</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,7 +1904,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Ek</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2105,44 +1915,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95823958</v>
+        <v>95823946</v>
       </c>
       <c r="B13" t="n">
-        <v>79135</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2152,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>710498.8260707015</v>
+        <v>710637</v>
       </c>
       <c r="R13" t="n">
-        <v>6401015.666107871</v>
+        <v>6400996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2185,24 +1990,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 12</t>
+          <t>Lauks änge (västra) 19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2227,22 +2022,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95823962</v>
+        <v>95808982</v>
       </c>
       <c r="B14" t="n">
-        <v>79122</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2250,34 +2040,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>734</v>
+        <v>1026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lauks änge (västra), Gtl</t>
+          <t>Lauks änge, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>710475.7280026325</v>
+        <v>710636</v>
       </c>
       <c r="R14" t="n">
-        <v>6400944.325201127</v>
+        <v>6400974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2307,26 +2097,11 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Lauks änge (västra) 10</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2336,57 +2111,67 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95823912</v>
+        <v>95823948</v>
       </c>
       <c r="B15" t="n">
-        <v>77870</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6430</v>
+        <v>1026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slät lönnlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bacidia fraxinea</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lönnr.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2396,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>710519.745415173</v>
+        <v>710637</v>
       </c>
       <c r="R15" t="n">
-        <v>6400964.290096581</v>
+        <v>6400996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,24 +2214,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 9</t>
+          <t>Lauks änge (västra) 19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2471,22 +2246,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95823959</v>
+        <v>95823923</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1348</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Hjälmbrosklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina baltica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Lettau</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2518,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>710498.8260707015</v>
+        <v>710603</v>
       </c>
       <c r="R16" t="n">
-        <v>6401015.666107871</v>
+        <v>6400919</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2551,24 +2321,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 12</t>
+          <t>Lauks änge (västra) 7</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2582,7 +2342,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2593,44 +2353,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95823913</v>
+        <v>95823918</v>
       </c>
       <c r="B17" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>738</v>
+        <v>1460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2640,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>710519.745415173</v>
+        <v>710603</v>
       </c>
       <c r="R17" t="n">
-        <v>6400964.290096581</v>
+        <v>6400919</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2673,24 +2428,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 9</t>
+          <t>Lauks änge (västra) 7</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2704,7 +2449,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2715,22 +2460,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95823954</v>
+        <v>95808984</v>
       </c>
       <c r="B18" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2738,37 +2478,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lauks änge (västra), Gtl</t>
+          <t>Lauks änge, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>710513.7985833556</v>
+        <v>710636</v>
       </c>
       <c r="R18" t="n">
-        <v>6401109.067499299</v>
+        <v>6400974</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2792,27 +2532,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lauks änge (västra) 16</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2824,57 +2549,67 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95823914</v>
+        <v>95823922</v>
       </c>
       <c r="B19" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2779</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2884,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>710519.745415173</v>
+        <v>710603</v>
       </c>
       <c r="R19" t="n">
-        <v>6400964.290096581</v>
+        <v>6400919</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2917,24 +2652,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 9</t>
+          <t>Lauks änge (västra) 7</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2948,7 +2673,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2959,57 +2684,52 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95823960</v>
+        <v>95808988</v>
       </c>
       <c r="B20" t="n">
-        <v>78031</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>125</v>
+        <v>6428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk lundlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scutula effusa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Rabenh.) Kistenich et al.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lauks änge (västra), Gtl</t>
+          <t>Lauks änge, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>710457.2776173789</v>
+        <v>710597</v>
       </c>
       <c r="R20" t="n">
-        <v>6400979.233525923</v>
+        <v>6401113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3039,24 +2759,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Lauks änge (västra) 11</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3068,73 +2778,80 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95808938</v>
+        <v>95823912</v>
       </c>
       <c r="B21" t="n">
-        <v>79130</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6000188</v>
+        <v>6430</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norsk belonia</t>
+          <t>Slät lönnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gyalecta nidarosiensis</t>
+          <t>Bacidia fraxinea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kindt) Baloch &amp; Lücking</t>
+          <t>Lönnr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lauks änge, Gtl</t>
+          <t>Lauks änge (västra), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>710604.5067657825</v>
+        <v>710519</v>
       </c>
       <c r="R21" t="n">
-        <v>6401046.345465234</v>
+        <v>6400964</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,24 +2881,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Steril. Tre bålar på asp.</t>
+          <t>Lauks änge (västra) 9</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3190,47 +2897,1798 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Ädellövskog/hassellund/lövänge</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>95823955</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79699</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6430</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Slät lönnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bacidia fraxinea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Lönnr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>710514</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6401109</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>95823954</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>710514</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6401109</v>
+      </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>95808995</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78753</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6435</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Diplotomma alboatrum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Flot.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lauks änge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>710481</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6400994</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Raul Vicente</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>95808998</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78753</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6435</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Diplotomma alboatrum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Flot.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lauks änge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>710580</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6400914</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>95823961</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78753</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6435</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vitskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Diplotomma alboatrum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Flot.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>710476</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6400945</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>95823916</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>710594</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6400909</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 8</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>95823920</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>710603</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6400919</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 7</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>95808986</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lauks änge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>710636</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6400974</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>95808996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lauks änge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>710474</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6400973</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>95808999</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lauks änge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>710580</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6400914</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Ädellövskog/hassellund/lövänge</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>95823914</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>710519</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6400964</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 9</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95823915</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>710594</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6400909</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 8</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>95823919</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>710603</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6400919</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 7</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>95823949</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>710642</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6401049</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>95823957</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>710552</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6401060</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>95823959</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>710499</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6401016</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lauks änge (västra) 12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43201-2023 artfynd.xlsx
+++ b/artfynd/A 43201-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808983</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808991</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808993</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823960</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823963</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808989</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823917</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823962</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1705,6 +1750,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808994</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823958</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,6 +1974,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823946</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808982</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823948</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2357,6 +2432,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823923</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2464,6 +2544,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823918</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2581,6 +2666,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808984</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2688,6 +2778,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823922</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2810,6 +2905,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808988</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2917,6 +3017,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823912</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823955</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823954</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3253,6 +3368,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808995</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3375,6 +3495,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808998</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3482,6 +3607,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823961</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3589,6 +3719,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823916</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3696,6 +3831,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823920</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3813,6 +3953,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808986</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3930,6 +4075,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808996</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4047,6 +4197,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95808999</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4154,6 +4309,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823914</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4261,6 +4421,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823915</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4368,6 +4533,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823919</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4475,6 +4645,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823949</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4582,6 +4757,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823957</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4689,8 +4869,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>